--- a/Data/Input/Insumo_RPA_One4Tech.xlsx
+++ b/Data/Input/Insumo_RPA_One4Tech.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2fed59b41ca10b7/Documents/UiPath/Desafio_One4Tech/Data/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{190B8149-719E-49AB-A596-064B06452233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBCCC952-ACC0-4E86-9761-8D6EFD84A359}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{190B8149-719E-49AB-A596-064B06452233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49D6BA5B-92FF-4724-9D71-EAFE905157E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33745035-6857-40F9-837B-CAE26AB317FD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Categoria</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>brazilian politics</t>
   </si>
 </sst>
 </file>
@@ -139,10 +142,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -558,8 +557,15 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
